--- a/output/full_scan/batch_seq7_2026-09-04.xlsx
+++ b/output/full_scan/batch_seq7_2026-09-04.xlsx
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>910.7770770948148</v>
+        <v>1110.777077094815</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1250</v>
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>65.79332478961447</v>
+        <v>65.79332483740251</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>25.05883998817341</v>
+        <v>25.05884004894727</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>2.279427217940052</v>
@@ -570,11 +570,11 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>25.20418480231454</v>
+        <v>25.20418479639992</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>877.3466288743235</v>
+        <v>1077.346628874324</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>219.5</v>
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>71.03630431555374</v>
+        <v>71.03630431596626</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>23.68247375999313</v>
+        <v>23.68247371229888</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>2.53016223577218</v>
@@ -623,11 +623,11 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>5.87421242652056</v>
+        <v>5.874212426539632</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>814.976847238793</v>
+        <v>984.9768472387932</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>239.5</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>61.72154758140791</v>
+        <v>61.72154765312801</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>29.4161019308</v>
+        <v>29.4161021538414</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>4.79934950564885</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>2.035784796682424</v>
+        <v>2.035784797159411</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6588</v>
+        <v>6538</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>東典光電</t>
+          <t>倉和</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>806.1041234580229</v>
+        <v>972.9889876452248</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>108.5</v>
+        <v>300</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,13 +711,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>57.84219886242423</v>
+        <v>83.4471172002778</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>25.27540620685041</v>
+        <v>43.48553286765915</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.5019404329525775</v>
+        <v>3.267959781026823</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>1</v>
@@ -729,11 +729,11 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.0480532120477308</v>
+        <v>8.329292826879339</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>784.1170664997646</v>
+        <v>899.1170664997646</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>541</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>62.76107634339677</v>
+        <v>62.76107634061611</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>30.98677736299089</v>
+        <v>30.98677747459312</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>1.148249649585411</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>9.387848054146538</v>
+        <v>9.387848054222856</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6584</v>
+        <v>6510</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>774.5683498690173</v>
+        <v>890.7947444333254</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>634</v>
+        <v>3350</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,49 +817,49 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>55.88525745251584</v>
+        <v>65.42169867427506</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>26.31783605104588</v>
+        <v>21.84800621254649</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.4468643689837512</v>
+        <v>1.838764276785146</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>5.535864411157</v>
+        <v>84.20985971708824</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6538</v>
+        <v>6670</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>倉和</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>772.9889876452249</v>
+        <v>890.2677734479244</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>300</v>
+        <v>275.5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,49 +870,49 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>83.44711720698221</v>
+        <v>55.30919552919838</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>43.48553279794773</v>
+        <v>27.71902646017224</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>3.267959781026823</v>
+        <v>0.5238300383446246</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>8.329292826631306</v>
+        <v>0.9309916706799424</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6805</v>
+        <v>6532</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>瑞耘</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>717.735806792581</v>
+        <v>868.7267402042155</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2200</v>
+        <v>98</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>62.40082272144787</v>
+        <v>67.07812580843313</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>29.83254525760915</v>
+        <v>42.7617930199003</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.270811626915471</v>
+        <v>1.137551708973316</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>15.38707080720613</v>
+        <v>0.9849895240050844</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6761</v>
+        <v>6530</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>穩得</t>
+          <t>創威</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>702.3232522493319</v>
+        <v>864.0227401844926</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>183</v>
+        <v>98.2</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>54.84805083213427</v>
+        <v>63.10354972257458</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>20.80282095109036</v>
+        <v>21.05231764529803</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.6089182242764262</v>
+        <v>1.202274018449257</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-0.1739847068966362</v>
+        <v>1.638676452825888</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6532</v>
+        <v>6588</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>瑞耘</t>
+          <t>東典光電</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>698.7267402042155</v>
+        <v>806.1041234580229</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>98</v>
+        <v>108.5</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>67.07812573006473</v>
+        <v>57.84219887271332</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>42.76179297958596</v>
+        <v>25.27540619144699</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.137551708973316</v>
+        <v>0.5019404329525775</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.9849895244629964</v>
+        <v>-0.0480532121431211</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6510</v>
+        <v>6515</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>690.7947444333254</v>
+        <v>784.2972849105632</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>3350</v>
+        <v>7075</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,49 +1082,49 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>65.42169866059562</v>
+        <v>58.03125600203337</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>21.84800622427393</v>
+        <v>15.82945766133382</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.838764276785146</v>
+        <v>1.556626703246167</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M12" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>84.20985972166713</v>
+        <v>128.8716250029451</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6651</v>
+        <v>6830</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>全宇昕</t>
+          <t>汎銓</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>689.5027365067482</v>
+        <v>779.9347232317386</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>151</v>
+        <v>597</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,49 +1135,49 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>59.82913475058799</v>
+        <v>71.50212429450085</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>29.28286072122813</v>
+        <v>32.42770195743759</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.4139446806816552</v>
+        <v>1.102624963630022</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.7715134242443833</v>
+        <v>15.55699858182012</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6716</v>
+        <v>6584</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>應廣</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>685.0970039648839</v>
+        <v>774.5683498690173</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>117</v>
+        <v>634</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,49 +1188,49 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>50.53527485922909</v>
+        <v>55.88525747689685</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>31.8469285727906</v>
+        <v>26.31783609517137</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>2.438135702396985</v>
+        <v>0.4468643689837512</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-1.727320649237374</v>
+        <v>5.535864410393749</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6739</v>
+        <v>6756</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>威鋒電子</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>674.978094452381</v>
+        <v>769.2124763949174</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1135</v>
+        <v>101.5</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>56.67518484005925</v>
+        <v>54.70060339996607</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>13.58928548431131</v>
+        <v>11.8425949691413</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.7553122596661782</v>
+        <v>1.614747289860984</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>16.14902800114535</v>
+        <v>0.179120978076078</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6530</v>
+        <v>6693</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>創威</t>
+          <t>廣閎科</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>664.0227401844926</v>
+        <v>766.9204524704926</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>98.2</v>
+        <v>181.5</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>63.10354964415068</v>
+        <v>52.84942486912706</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>21.05231755748213</v>
+        <v>15.29910533910181</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.202274018449257</v>
+        <v>1.706621824519028</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>1.638676453112075</v>
+        <v>2.011321731489742</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6693</v>
+        <v>6505</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>廣閎科</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>651.9204524704926</v>
+        <v>763.8825866098557</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>181.5</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,29 +1347,29 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>52.84942486396994</v>
+        <v>59.70857504075566</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>15.29910531247818</v>
+        <v>30.05902497224401</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.706621824519028</v>
+        <v>0.6831613416389891</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>2.011321731413426</v>
+        <v>0.5581303520613219</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>645.8963336685791</v>
+        <v>760.8963336685791</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>56</v>
@@ -1403,7 +1403,7 @@
         <v>56.6920962311553</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>10.58474182395625</v>
+        <v>10.584741779821</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>0.951642307129452</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.24698282903989</v>
+        <v>0.2469828289540325</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6533</v>
+        <v>6829</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>千附精密</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>639.1791771069107</v>
+        <v>753.8258777860706</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>264</v>
+        <v>243.5</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>63.12466629906865</v>
+        <v>59.09855852521245</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>20.47166314870252</v>
+        <v>19.86177957220759</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.4436444839502867</v>
+        <v>0.5333153924204413</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-0.204646140533935</v>
+        <v>1.590326901959683</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6829</v>
+        <v>6669</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>千附精密</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>638.8258777860706</v>
+        <v>723.7536694699183</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>243.5</v>
+        <v>2565</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,49 +1506,49 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>59.09855851832322</v>
+        <v>26.88224247903664</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>19.86177961494853</v>
+        <v>35.58503139492908</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.5333153924204413</v>
+        <v>1.848048283296152</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>1.59032690215048</v>
+        <v>-509.518083437959</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6668</v>
+        <v>6491</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>中揚光</t>
+          <t>晶碩</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>637.5138969911975</v>
+        <v>721.9980998688114</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>42.6</v>
+        <v>385</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>62.49685925276667</v>
+        <v>57.47623942152057</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>33.9026271440223</v>
+        <v>28.22525476431032</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.6981995653435167</v>
+        <v>0.4839622884050794</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.6247231804272888</v>
+        <v>0.240673507751012</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6670</v>
+        <v>6805</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>620.2677734479244</v>
+        <v>717.735806792581</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>275.5</v>
+        <v>2200</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>55.30919556731959</v>
+        <v>62.40082272144787</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>27.7190264252033</v>
+        <v>29.83254525760915</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.5238300383446246</v>
+        <v>0.270811626915471</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.9309916714432004</v>
+        <v>15.38707080720613</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6581</v>
+        <v>6642</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>鋼聯</t>
+          <t>富致</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>607.0480103694296</v>
+        <v>706.1489221021751</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>109.5</v>
+        <v>83.3</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>59.39485458857403</v>
+        <v>56.66257643539534</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>21.52340527595239</v>
+        <v>19.03709848088013</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.6967015575906447</v>
+        <v>0.6475493140068476</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.0693563325283385</v>
+        <v>0.1710230193174582</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6782</v>
+        <v>6761</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>視陽</t>
+          <t>穩得</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>602.3481428514555</v>
+        <v>702.3232522493319</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>229.5</v>
+        <v>183</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>56.23585159300883</v>
+        <v>54.84805085130996</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>29.9414139273715</v>
+        <v>20.80282094650043</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.6021427798862404</v>
+        <v>0.6089182242764262</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.963324311985545</v>
+        <v>-0.1739847071446938</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6642</v>
+        <v>6651</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>富致</t>
+          <t>全宇昕</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>591.1489221021751</v>
+        <v>689.5027365067482</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>83.3</v>
+        <v>151</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>56.66257639215198</v>
+        <v>59.82913477468127</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>19.03709845346265</v>
+        <v>29.28286074279931</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.6475493140068476</v>
+        <v>0.4139446806816552</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.1710230195082427</v>
+        <v>0.7715134239772494</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6669</v>
+        <v>6680</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>鑫創電子</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>564.4399562934494</v>
+        <v>685.3688634400471</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>2565</v>
+        <v>54.7</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>26.88224246389496</v>
+        <v>52.67398805227731</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>35.58503123165769</v>
+        <v>7.875835039091399</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.59852764285545</v>
+        <v>1.627646326276463</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-509.5180834112477</v>
+        <v>-0.2330381597743365</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>volume_break, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, breakout_volume_confirm, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6771</v>
+        <v>6716</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>平和環保-創</t>
+          <t>應廣</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>561.2241300555711</v>
+        <v>685.0970039648839</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>41.8</v>
+        <v>117</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>57.22295242388153</v>
+        <v>50.53527486743676</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>31.65416715044317</v>
+        <v>31.84692877664996</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.5862101303170097</v>
+        <v>2.438135702396985</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.0985164554919416</v>
+        <v>-1.727320649580781</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6505</v>
+        <v>6668</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>中揚光</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>553.8825866098557</v>
+        <v>677.5138969911975</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>78.09999999999999</v>
+        <v>42.6</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>59.7085750512532</v>
+        <v>62.49685926397307</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>30.05902497428582</v>
+        <v>33.90262713889607</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.6831613416389891</v>
+        <v>0.6981995653435167</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.5581303519659169</v>
+        <v>0.624723180312805</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6491</v>
+        <v>6771</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>晶碩</t>
+          <t>平和環保-創</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>546.9980998688116</v>
+        <v>676.2241300555711</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>385</v>
+        <v>41.8</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>57.47623933041678</v>
+        <v>57.22295246701989</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>28.225254729484</v>
+        <v>31.65416716178537</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.4839622884050794</v>
+        <v>0.5862101303170097</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.2406735097544015</v>
+        <v>-0.09851645556826071</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6830</v>
+        <v>6666</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>汎銓</t>
+          <t>羅麗芬-KY</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>539.9347232317386</v>
+        <v>675.8966477985482</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>597</v>
+        <v>44.35</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>71.50212427862326</v>
+        <v>54.79808904350291</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>32.42770190513263</v>
+        <v>15.66262812159645</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.102624963630022</v>
+        <v>0.9436109169524862</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>15.55699858248792</v>
+        <v>0.0776167362527081</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6548</v>
+        <v>6739</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>長科*</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>533.0277379785298</v>
+        <v>674.9780944523816</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>75.2</v>
+        <v>1135</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,66 +2089,66 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>54.39568724326024</v>
+        <v>56.67518490002759</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>11.99740610019343</v>
+        <v>13.58928559801674</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.40208289024347</v>
+        <v>0.7553122596661782</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.3676601226336523</v>
+        <v>16.14902799475366</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6806</v>
+        <v>6533</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>森崴能源</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>528.7768356926886</v>
+        <v>669.1791771069107</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>3.51</v>
+        <v>264</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G32" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>31.6950419391173</v>
+        <v>63.12466645850242</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>32.59320941589322</v>
+        <v>20.47166321002143</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>2.013053626871306</v>
+        <v>0.4436444839502867</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.4112821789872449</v>
+        <v>-0.204646142155676</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6672</v>
+        <v>6579</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>騰輝電子-KY</t>
+          <t>研揚</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>522.6195591780119</v>
+        <v>663.0787403124872</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>289</v>
+        <v>150.5</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>59.09837638976047</v>
+        <v>47.47481500533405</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>16.80874496678971</v>
+        <v>16.0755953984139</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.25061225567909</v>
+        <v>1.109224118385341</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.3804394642746196</v>
+        <v>0.1007319167159201</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, stronger_than_market, dealer_buy_3d, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6666</v>
+        <v>6743</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>羅麗芬-KY</t>
+          <t>安普新</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>520.8966477985483</v>
+        <v>657.5900517092545</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>44.35</v>
+        <v>28.6</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>54.79808918250577</v>
+        <v>58.64860767145612</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>15.6626282871549</v>
+        <v>21.73009815697395</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.9436109169524862</v>
+        <v>1.011365614165625</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.077616736128695</v>
+        <v>0.4494574519843652</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6741</v>
+        <v>6782</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>91APP*-KY</t>
+          <t>視陽</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>520.2923470934048</v>
+        <v>657.3481428514555</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>60</v>
+        <v>229.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>61.13031504529543</v>
+        <v>56.23585162904036</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>30.66151603311324</v>
+        <v>29.94141393074881</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.4034831153047392</v>
+        <v>0.6021427798862404</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.4914542247280877</v>
+        <v>0.9633243113177556</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6680</v>
+        <v>6548</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>鑫創電子</t>
+          <t>長科*</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>515.3688634400471</v>
+        <v>648.0277379785298</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>54.7</v>
+        <v>75.2</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,49 +2354,49 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>52.67398789630584</v>
+        <v>54.3956872485586</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>7.875834473382538</v>
+        <v>11.99740615816963</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.627646326276463</v>
+        <v>1.40208289024347</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M36" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.233038145960819</v>
+        <v>0.3676601225764153</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>volume_break, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6756</v>
+        <v>6741</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>威鋒電子</t>
+          <t>91APP*-KY</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>504.2124763949171</v>
+        <v>635.2923470934048</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>101.5</v>
+        <v>60</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>54.70060333462659</v>
+        <v>61.13031512052103</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>11.8425949419615</v>
+        <v>30.66151591829486</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.614747289860984</v>
+        <v>0.4034831153047392</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.1791209784195038</v>
+        <v>0.4914542246517722</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6517</v>
+        <v>6568</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>保勝光學</t>
+          <t>宏觀</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>504.0436061391839</v>
+        <v>630.6571571941168</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>69.2</v>
+        <v>137</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>53.20083671373738</v>
+        <v>51.58194211054728</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>18.64772350568532</v>
+        <v>32.937689451584</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.687456169487922</v>
+        <v>0.9852154647052136</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.2736921311155906</v>
+        <v>1.828903346951436</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6568</v>
+        <v>6486</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>宏觀</t>
+          <t>互動</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>490.6571571941167</v>
+        <v>606.0965149495335</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>137</v>
+        <v>82.2</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>51.5819420745542</v>
+        <v>66.99609376069023</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>32.9376893471098</v>
+        <v>33.03096314862353</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.9852154647052136</v>
+        <v>2.209651494953342</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,11 +2531,11 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>1.828903347905388</v>
+        <v>1.143901572472896</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>482.9918619806096</v>
+        <v>597.9918619806095</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>320</v>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>41.01366564093771</v>
+        <v>41.01366564472399</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>14.0264824258422</v>
+        <v>14.02648242092687</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>0.9120661712059452</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-8.549586223185761</v>
+        <v>-8.549586223662741</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6743</v>
+        <v>6655</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>安普新</t>
+          <t>科定</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>477.5900517092544</v>
+        <v>589.1816846324959</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>28.6</v>
+        <v>117.5</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>58.64860761680799</v>
+        <v>51.91465271746318</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>21.73009815697396</v>
+        <v>16.93522799171799</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.011365614165625</v>
+        <v>3.893559808728874</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,11 +2637,11 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.4494574519939032</v>
+        <v>-4.083206613221137</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, williams_r_recovery, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -2658,7 +2658,7 @@
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>471.921053783868</v>
+        <v>586.9210537838679</v>
       </c>
       <c r="E42" s="2" t="n">
         <v>138.5</v>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>52.01290625364933</v>
+        <v>52.01290631651121</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>13.20401223541605</v>
+        <v>13.2040122562272</v>
       </c>
       <c r="J42" s="2" t="n">
         <v>0.8521034437048995</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.3801075928785995</v>
+        <v>-0.3801075929739885</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6753</v>
+        <v>6581</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>龍德造船</t>
+          <t>鋼聯</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>460.0557701975528</v>
+        <v>577.0480103694296</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>137.5</v>
+        <v>109.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>46.61868447588115</v>
+        <v>59.39485465140835</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>23.66498755149125</v>
+        <v>21.52340536183408</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.3698528411434742</v>
+        <v>0.6967015575906447</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,11 +2743,11 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.7911681100262672</v>
+        <v>0.0693563323375372</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>456.5858761321773</v>
+        <v>571.5858761321773</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>33.05</v>
@@ -2778,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>49.44035589075914</v>
+        <v>49.44035623023424</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>26.45960015833929</v>
+        <v>26.4596002525899</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>1.449443408636225</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.1253788388709932</v>
+        <v>0.1253788387183525</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6834</v>
+        <v>6768</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>天二科技</t>
+          <t>志強-KY</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>454.6686842042984</v>
+        <v>570.093359766298</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>94</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>50.36238053683934</v>
+        <v>36.81295882330275</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>9.595146881744764</v>
+        <v>28.67087954059228</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.073567396862947</v>
+        <v>0.3746237709254016</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.06947621241863559</v>
+        <v>0.2235558351952111</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6768</v>
+        <v>6706</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>志強-KY</t>
+          <t>惠特</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>440.093359766298</v>
+        <v>548.9604167521899</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>64.09999999999999</v>
+        <v>127</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>36.81295861527901</v>
+        <v>55.83366465623283</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>28.67087958079723</v>
+        <v>16.08961454775243</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.3746237709254016</v>
+        <v>0.8302343213151002</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.2235558357675988</v>
+        <v>1.225171618813377</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6486</v>
+        <v>6672</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>互動</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>436.0965149495334</v>
+        <v>547.6195591780119</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>82.2</v>
+        <v>289</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>66.99609401680488</v>
+        <v>59.09837639979121</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>33.03096313450352</v>
+        <v>16.80874498610398</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>2.209651494953342</v>
+        <v>1.25061225567909</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>1.14390157262553</v>
+        <v>-0.380439464579883</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6655</v>
+        <v>6789</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>科定</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>434.1816846324962</v>
+        <v>537.3093279324078</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>117.5</v>
+        <v>468</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>51.91465272156218</v>
+        <v>53.66654310123386</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>16.93522798031682</v>
+        <v>17.62896511375533</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>3.893559808728874</v>
+        <v>0.744592620321891</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-4.083206613507339</v>
+        <v>5.97322921567287</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6579</v>
+        <v>6526</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>研揚</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>433.0787403124872</v>
+        <v>530.0826253187499</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>150.5</v>
+        <v>635</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>47.47481501260469</v>
+        <v>55.77770578043164</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>16.07559530693149</v>
+        <v>16.17969600482686</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.109224118385341</v>
+        <v>0.7613955461579384</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,48 +3061,48 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.1007319166205258</v>
+        <v>6.186413980651649</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, williams_r_recovery</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6515</v>
+        <v>6806</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>森崴能源</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>429.2972849105612</v>
+        <v>528.7768356926886</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>7075</v>
+        <v>3.51</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G50" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>58.03125599155059</v>
+        <v>31.6950221152637</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>15.82945758618664</v>
+        <v>32.59323562498059</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.556626703246167</v>
+        <v>2.013053626871306</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>128.8716250077149</v>
+        <v>0.4112822342230751</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6613</v>
+        <v>6488</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>朋億*</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>427.6597647239031</v>
+        <v>521.8273029169379</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>258.5</v>
+        <v>981</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,49 +3149,49 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>42.55602440745112</v>
+        <v>50.19535125989793</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>10.84982490584902</v>
+        <v>8.939851291541959</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.4191452402068097</v>
+        <v>0.8227219015470496</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>2.231880614843002</v>
+        <v>3.829906829303347</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6488</v>
+        <v>6683</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>雍智科技</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>406.8273029169379</v>
+        <v>521.2578435884891</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>981</v>
+        <v>1360</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,49 +3202,49 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>50.19535125464022</v>
+        <v>55.74166871266846</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>8.939851284211771</v>
+        <v>16.25561381784705</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.8227219015470496</v>
+        <v>1.766224756972206</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>3.829906830543592</v>
+        <v>33.54512391088785</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6512</v>
+        <v>6753</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>啟發電</t>
+          <t>龍德造船</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>396.6706257190385</v>
+        <v>515.0557701975528</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>20.2</v>
+        <v>137.5</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>52.56398963015185</v>
+        <v>46.61868447912755</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>9.912067276789749</v>
+        <v>23.66498753804372</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.8737341987866486</v>
+        <v>0.3698528411434742</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.1715196880222464</v>
+        <v>-0.791168109949961</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6754</v>
+        <v>6834</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>匯僑設計</t>
+          <t>天二科技</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>395.3781282608039</v>
+        <v>514.6686842042984</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>48.76585690357718</v>
+        <v>50.36238054778669</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>12.18515800717123</v>
+        <v>9.595146872742852</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.2330014590542421</v>
+        <v>1.073567396862947</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.0181839165647443</v>
+        <v>-0.0694762125044987</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6706</v>
+        <v>6517</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>惠特</t>
+          <t>保勝光學</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>393.9604167521896</v>
+        <v>504.0436061391839</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>127</v>
+        <v>69.2</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>55.83366465041517</v>
+        <v>53.20083674061718</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>16.08961448891499</v>
+        <v>18.64772345462071</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.8302343213151002</v>
+        <v>0.687456169487922</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>1.225171619099579</v>
+        <v>0.2736921309629594</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6573</v>
+        <v>6589</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>虹揚-KY</t>
+          <t>台康生技</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>390.682510335356</v>
+        <v>499.6483906480881</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>16.95</v>
+        <v>48.05</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>46.20459064791096</v>
+        <v>46.16990378460952</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>18.81405602307576</v>
+        <v>19.84818199481529</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.5578310453403426</v>
+        <v>0.5370411760092406</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.0329051506920544</v>
+        <v>-0.3893177398551864</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6719</v>
+        <v>6658</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>聯策</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>389.4925394107825</v>
+        <v>499.1121993265826</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>40.1652914066293</v>
+        <v>56.55405431500935</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>23.30653633530829</v>
+        <v>17.04104134730213</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.5571751593557999</v>
+        <v>0.664209184466</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>1.039607280699984</v>
+        <v>2.563539542473526</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6477</v>
+        <v>6531</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>安集</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>388.1654770914292</v>
+        <v>483.7196456472892</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>34.8</v>
+        <v>911</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,49 +3520,49 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>43.96577325545638</v>
+        <v>52.48483762094607</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>17.67786293131863</v>
+        <v>10.12834700281057</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.2167178293393814</v>
+        <v>0.8366478355172018</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M58" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.2485911829456975</v>
+        <v>5.039184350976173</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6577</v>
+        <v>6754</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>勁豐</t>
+          <t>匯僑設計</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>387.2615093667466</v>
+        <v>475.378128260804</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>80.3</v>
+        <v>42</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,49 +3573,49 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>50.35827463141541</v>
+        <v>48.76585688954224</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>18.81973988658675</v>
+        <v>12.18515799731984</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.4666063993954439</v>
+        <v>0.2330014590542421</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M59" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.1015719942846625</v>
+        <v>0.0181839165075091</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, invest_trust_buy_2d</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6770</v>
+        <v>6757</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>台灣虎航-創</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>386.7614752700827</v>
+        <v>461.8732572746874</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>68.5</v>
+        <v>55.9</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>49.29875340935725</v>
+        <v>48.89555096128765</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>10.64375729227818</v>
+        <v>9.573622615665132</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.4241743765542351</v>
+        <v>0.365755894091412</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.206943951193148</v>
+        <v>0.0407129555224381</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6831</v>
+        <v>6821</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>邁科</t>
+          <t>聯寶</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>385.860749918112</v>
+        <v>446.280524191152</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>605</v>
+        <v>42.4</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>47.83465637425189</v>
+        <v>47.6187383669683</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>12.85369401916643</v>
+        <v>14.26515376350118</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.9752849979600204</v>
+        <v>0.8271488053866485</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>2.986599366342034</v>
+        <v>0.4129587660777596</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6788</v>
+        <v>6792</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>詠業</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>382.7308514638012</v>
+        <v>442.4987014463039</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>352.5</v>
+        <v>60.1</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>46.04739081647149</v>
+        <v>57.11774289176227</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>17.51520625950711</v>
+        <v>14.46876906531824</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.237127484658828</v>
+        <v>0.5060843750507257</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>1.179015956960915</v>
+        <v>0.1412149612493433</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6789</v>
+        <v>6831</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>邁科</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>382.3093279324077</v>
+        <v>435.860749918112</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>468</v>
+        <v>605</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>53.6665430497916</v>
+        <v>47.83465638671221</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>17.62896508862077</v>
+        <v>12.85369387043594</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.744592620321891</v>
+        <v>0.9752849979600204</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>5.973229217103813</v>
+        <v>2.986599363766334</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6691</v>
+        <v>6613</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>朋億*</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>379.9120417468843</v>
+        <v>427.6597647239031</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>619</v>
+        <v>258.5</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>40.99338874446567</v>
+        <v>42.55602436038201</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>22.5433198701164</v>
+        <v>10.84982494358365</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.001542890779656</v>
+        <v>0.4191452402068097</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-2.85512087024108</v>
+        <v>2.231880616273921</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6525</v>
+        <v>6770</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>捷敏-KY</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>363.2747976222871</v>
+        <v>426.7614752700827</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>138</v>
+        <v>68.5</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>46.58116742001801</v>
+        <v>49.29875341050531</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>8.89743683460325</v>
+        <v>10.64375729713113</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.4227635777579704</v>
+        <v>0.4241743765542351</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.0005753536387329</v>
+        <v>-0.2069439511836071</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6582</v>
+        <v>6525</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>申豐</t>
+          <t>捷敏-KY</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>356.2080514070811</v>
+        <v>423.2747976222871</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>31.9</v>
+        <v>138</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>47.00666689215932</v>
+        <v>46.58116742841852</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>23.76888694379385</v>
+        <v>8.897436873415998</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.5524600128333783</v>
+        <v>0.4227635777579704</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.0346766701098519</v>
+        <v>0.0005753535814752</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6526</v>
+        <v>6691</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>355.0826253187491</v>
+        <v>419.9120417468843</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>635</v>
+        <v>619</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,49 +3997,49 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>55.77770568558616</v>
+        <v>40.99338877806176</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>16.17969593706882</v>
+        <v>22.54331987117377</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.7613955461579384</v>
+        <v>1.001542890779656</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>6.186413986184787</v>
+        <v>-2.8551208713859</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6794</v>
+        <v>6573</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>向榮生技-創</t>
+          <t>虹揚-KY</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>350.5901395432002</v>
+        <v>410.682510335356</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>73.7</v>
+        <v>16.95</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>44.82501211918655</v>
+        <v>46.20459065011775</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>20.14434460566161</v>
+        <v>18.81405609516334</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.6283490523271628</v>
+        <v>0.5578310453403426</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.2533248348354333</v>
+        <v>0.0329051506882347</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6664</v>
+        <v>6592</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>群翊</t>
+          <t>和潤企業</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>350.4092868299297</v>
+        <v>408.8844887923029</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>355.5</v>
+        <v>61</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,49 +4103,49 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>50.48555804056262</v>
+        <v>50.26696844235739</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>13.8540422910121</v>
+        <v>10.31602165045927</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1.396320353310223</v>
+        <v>0.7135983143758733</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L69" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M69" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>2.260960110102356</v>
+        <v>-0.0046224261718501</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6674</v>
+        <v>6708</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>鋐寶科技</t>
+          <t>天擎</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>350.2904645901655</v>
+        <v>406.7564987944944</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>15.65</v>
+        <v>38.75</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>46.97288362589344</v>
+        <v>52.02395259525414</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>21.4913687108017</v>
+        <v>7.431870479668045</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.6594643671225853</v>
+        <v>0.1751893526709839</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.0337867913414063</v>
+        <v>0.0197837638628641</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6684</v>
+        <v>6512</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>安格</t>
+          <t>啟發電</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>344.2830535232504</v>
+        <v>396.6706257190385</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>46.3</v>
+        <v>20.2</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>43.9570750422973</v>
+        <v>52.56398962784893</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>11.17258366872978</v>
+        <v>9.912067218784449</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.4118658514242276</v>
+        <v>0.8737341987866486</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.09916102933688251</v>
+        <v>0.1715196880794843</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6692</v>
+        <v>6781</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>進能服</t>
+          <t>AES-KY</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>344.2700653980651</v>
+        <v>390.8034999033849</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>23.05</v>
+        <v>1115</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>47.06532516302706</v>
+        <v>53.15742275978894</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>8.808103276895823</v>
+        <v>12.57149911629963</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.9742671035784352</v>
+        <v>0.4770190780611807</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.1122928248442621</v>
+        <v>1.32010585953638</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6821</v>
+        <v>6577</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>聯寶</t>
+          <t>勁豐</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>331.280524191152</v>
+        <v>387.2615093667466</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>42.4</v>
+        <v>80.3</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,49 +4315,49 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>47.61873835179068</v>
+        <v>50.35827460057912</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>14.26515375061738</v>
+        <v>18.81973989406226</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.8271488053866485</v>
+        <v>0.4666063993954439</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L73" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M73" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.4129587661159175</v>
+        <v>-0.1015719941892774</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6781</v>
+        <v>6788</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>AES-KY</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>330.8034999033849</v>
+        <v>382.7308514638012</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>1115</v>
+        <v>352.5</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>53.15742259318832</v>
+        <v>46.04739096209117</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>12.57149909379684</v>
+        <v>17.51520633799684</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.4770190780611807</v>
+        <v>1.237127484658828</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>1.320105863352264</v>
+        <v>1.179015954957622</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6683</v>
+        <v>6719</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>雍智科技</t>
+          <t>力智</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>321.2578435884891</v>
+        <v>359.4925394107825</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>1360</v>
+        <v>191</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>55.74166871401793</v>
+        <v>40.16529151354112</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>16.25561376160596</v>
+        <v>23.30653640917805</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.766224756972206</v>
+        <v>0.5571751593557999</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>33.5451239103154</v>
+        <v>1.0396072800322</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6792</v>
+        <v>6477</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>詠業</t>
+          <t>安集</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>307.4987014463039</v>
+        <v>358.1654770914292</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>60.1</v>
+        <v>34.8</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>57.11774274791428</v>
+        <v>43.96577322935612</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>14.46876899737562</v>
+        <v>17.6778628854211</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.5060843750507257</v>
+        <v>0.2167178293393814</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.141214961468752</v>
+        <v>-0.248591182869381</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6561</v>
+        <v>6645</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>是方</t>
+          <t>金萬林-創</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>307.4650718147513</v>
+        <v>354.4226384607074</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>322</v>
+        <v>12.35</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,49 +4527,49 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>47.03523676982447</v>
+        <v>36.1518610189221</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>8.754218143303566</v>
+        <v>31.09812239795745</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.8400263852242744</v>
+        <v>1.722665414112947</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.4324726408624357</v>
+        <v>-0.0199233836956641</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6757</v>
+        <v>6664</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>台灣虎航-創</t>
+          <t>群翊</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>306.8732572746874</v>
+        <v>350.4092868299301</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>55.9</v>
+        <v>355.5</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,49 +4580,49 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>48.89555084878983</v>
+        <v>50.48555810510417</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>9.573622587967929</v>
+        <v>13.85404226881502</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.365755894091412</v>
+        <v>1.396320353310223</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.0407129556941532</v>
+        <v>2.26096010933915</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6763</v>
+        <v>6674</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>綠界科技</t>
+          <t>鋐寶科技</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>303.0051937688389</v>
+        <v>350.2904645901657</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>41.25</v>
+        <v>15.65</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,49 +4633,49 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>40.98044448095619</v>
+        <v>46.97288374883168</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>21.1498966396502</v>
+        <v>21.49136869286244</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.141740582453646</v>
+        <v>0.6594643671225853</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L79" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M79" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.0265217012706764</v>
+        <v>0.0337867914081856</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6541</v>
+        <v>6684</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>泰福-KY</t>
+          <t>安格</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>297.3249704511079</v>
+        <v>344.2830535232504</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>31.7</v>
+        <v>46.3</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>27.95905933914752</v>
+        <v>43.95707510560689</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>22.72346614096863</v>
+        <v>11.17258366276973</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1.172233537476773</v>
+        <v>0.4118658514242276</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.49808936758081</v>
+        <v>0.0991610290316095</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6645</v>
+        <v>6692</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>金萬林-創</t>
+          <t>進能服</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>294.4226384607075</v>
+        <v>344.2700653980651</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>12.35</v>
+        <v>23.05</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>36.15186066111914</v>
+        <v>47.06532525527702</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>31.09812231624648</v>
+        <v>8.808103291833163</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.722665414112947</v>
+        <v>0.9742671035784352</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.0199233834953308</v>
+        <v>-0.1122928250255123</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6720</v>
+        <v>6679</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>久昌</t>
+          <t>鈺太</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>292.2184911289792</v>
+        <v>342.0480078519417</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>131.5</v>
+        <v>206</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>41.61181926716931</v>
+        <v>46.45630032413585</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>29.31362369659369</v>
+        <v>18.44206098691678</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1.597860297991328</v>
+        <v>2.775821844819192</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.2575229366406981</v>
+        <v>2.221960487688521</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6658</v>
+        <v>6541</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>聯策</t>
+          <t>泰福-KY</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>289.1121993265826</v>
+        <v>337.3249704511079</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>178</v>
+        <v>31.7</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>56.5540542896479</v>
+        <v>27.95905952100217</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>17.04104131967689</v>
+        <v>22.72346621435772</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.664209184466</v>
+        <v>1.172233537476773</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>2.5635395429696</v>
+        <v>-0.4980893683821437</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6597</v>
+        <v>6560</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>立誠</t>
+          <t>欣普羅</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>287.4043295649925</v>
+        <v>332.0693147147454</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>72.90000000000001</v>
+        <v>31.4</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>52.07485138656673</v>
+        <v>50.88874778168615</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>7.633320200984113</v>
+        <v>15.40785884856101</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.552944429084877</v>
+        <v>0.2716117269122797</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>2.452115515524938</v>
+        <v>0.6269876595473467</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6558</v>
+        <v>6582</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>興能高</t>
+          <t>申豐</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>284.2977921424388</v>
+        <v>326.2080514070811</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>24.75</v>
+        <v>31.9</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>42.81023805310104</v>
+        <v>47.00666683303904</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>26.47946315419792</v>
+        <v>23.76888697554552</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.6322989920657168</v>
+        <v>0.5524600128333783</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.0495044906828783</v>
+        <v>-0.0346766700716966</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6796</v>
+        <v>6695</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>晉弘</t>
+          <t>芯鼎</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>280.4773953851893</v>
+        <v>323.9260411213474</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>59.7</v>
+        <v>49.5</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>48.45798817248365</v>
+        <v>49.19785747570257</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>26.9009053949516</v>
+        <v>13.39133526209634</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.5832953328936372</v>
+        <v>0.4674290607110941</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.3441905780407968</v>
+        <v>0.3553813038803617</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6550</v>
+        <v>6534</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>北極星藥業-KY</t>
+          <t>正瀚-創</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>279.9330652852395</v>
+        <v>321.247795945387</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>10.35</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>39.72228859758582</v>
+        <v>41.7047016245793</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>20.96825047584552</v>
+        <v>11.43073395668594</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.541870449206857</v>
+        <v>0.2935142901853669</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.0294188001955319</v>
+        <v>-0.1584133367955955</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6589</v>
+        <v>6794</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>台康生技</t>
+          <t>向榮生技-創</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>274.6483906480881</v>
+        <v>320.5901395432002</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>48.05</v>
+        <v>73.7</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>46.16990365890346</v>
+        <v>44.82501211455214</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>19.84818199635248</v>
+        <v>20.144344671192</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.5370411760092406</v>
+        <v>0.6283490523271628</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.3893177396834713</v>
+        <v>0.2533248348544952</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6811</v>
+        <v>6796</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>宏碁資訊</t>
+          <t>晉弘</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>273.412515492615</v>
+        <v>320.4773953851893</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>222</v>
+        <v>59.7</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>45.46353475277022</v>
+        <v>48.45798823452299</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>9.802303206664511</v>
+        <v>26.9009055826183</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.4786259270436845</v>
+        <v>0.5832953328936372</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>1</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.717647232158299</v>
+        <v>-0.3441905782506717</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6570</v>
+        <v>6671</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>維田</t>
+          <t>三能-KY</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>272.1159251190593</v>
+        <v>309.3486770750298</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>51.6</v>
+        <v>23.2</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>45.06690625219606</v>
+        <v>51.1309377157588</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>15.64369276271217</v>
+        <v>16.46739667364759</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.5777961910212658</v>
+        <v>0.3944688681956351</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.4232510842959058</v>
+        <v>0.08115999314168269</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6591</v>
+        <v>6561</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>動力-KY</t>
+          <t>是方</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>270.484827357201</v>
+        <v>307.4650718147513</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>42.7</v>
+        <v>322</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,49 +5269,49 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>39.1361732598715</v>
+        <v>47.03523694817902</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>28.96675883441058</v>
+        <v>8.754218147097522</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.5846792014163869</v>
+        <v>0.8400263852242744</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M91" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.1353179684698149</v>
+        <v>0.4324726392406433</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6725</v>
+        <v>6763</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>矽科宏晟</t>
+          <t>綠界科技</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>269.3087497539195</v>
+        <v>303.005193768839</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>225</v>
+        <v>41.25</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,25 +5322,25 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>40.10002392246756</v>
+        <v>40.98044374714692</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>31.04235576345</v>
+        <v>21.14989703885377</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1.071243921483647</v>
+        <v>1.141740582453646</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>1.901786325012987</v>
+        <v>-0.0265217005075016</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -5350,21 +5350,21 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6708</v>
+        <v>6657</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>天擎</t>
+          <t>華安</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>266.7564987944938</v>
+        <v>301.3802210558334</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>38.75</v>
+        <v>30</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>52.02395259220875</v>
+        <v>42.60209990432912</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>7.431870482693405</v>
+        <v>20.737602547224</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.1751893526709839</v>
+        <v>1.603059282166191</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.0197837639010187</v>
+        <v>0.1779204312733219</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6823</v>
+        <v>6720</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>濾能</t>
+          <t>久昌</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>265.8100407292235</v>
+        <v>292.2184911289804</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>60.3</v>
+        <v>131.5</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>39.57222993267221</v>
+        <v>41.61181926716931</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>20.07982884434463</v>
+        <v>29.31362371228204</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.6144895466539037</v>
+        <v>1.597860297991328</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>1</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.128853233123287</v>
+        <v>-0.2575229368314662</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6657</v>
+        <v>6597</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>華安</t>
+          <t>立誠</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>261.3802210558333</v>
+        <v>287.4043295649902</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>30</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>42.60209977059076</v>
+        <v>52.07485138346944</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>20.73760252272631</v>
+        <v>7.633320261831108</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1.603059282166191</v>
+        <v>0.552944429084877</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.1779204315022762</v>
+        <v>2.452115515620332</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6776</v>
+        <v>6742</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>澤米</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>244.1328458207489</v>
+        <v>282.6369803413826</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>53.1</v>
+        <v>44.95</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>44.0805985576516</v>
+        <v>49.10005234627175</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>15.39007400018334</v>
+        <v>18.68646886110467</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.6461886850912305</v>
+        <v>0.8627276410185265</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.005513383274361</v>
+        <v>0.4896770783957145</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6585</v>
+        <v>6550</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>鼎基</t>
+          <t>北極星藥業-KY</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>237.0933256225154</v>
+        <v>279.9330652852395</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>113</v>
+        <v>10.35</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>44.51826426954816</v>
+        <v>39.72228856588911</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>18.55174634866521</v>
+        <v>20.96825047966746</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.7401015586510881</v>
+        <v>0.541870449206857</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.1051054645326015</v>
+        <v>-0.0294188002050721</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6690</v>
+        <v>6585</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>鼎基</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>231.5569080063362</v>
+        <v>277.0933256225153</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>162.5</v>
+        <v>113</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>45.00451369332657</v>
+        <v>44.51826432999364</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>9.367609957451904</v>
+        <v>18.55174634866521</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.33617506828403</v>
+        <v>0.7401015586510881</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.069957672549256</v>
+        <v>-0.1051054647615603</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6735</v>
+        <v>6811</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>美達科技</t>
+          <t>宏碁資訊</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>230.4312222384285</v>
+        <v>273.412515492615</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>63.3</v>
+        <v>222</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>45.32496334093573</v>
+        <v>45.46353484325348</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>14.88827618737424</v>
+        <v>9.802303198500423</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.8151446085280742</v>
+        <v>0.4786259270436845</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>1</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.5866663720149692</v>
+        <v>-0.7176472333030645</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6531</v>
+        <v>6570</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>維田</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>228.7196456472892</v>
+        <v>272.1159251190593</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>911</v>
+        <v>51.6</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>52.48483762792199</v>
+        <v>45.06690622562049</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>10.12834717575047</v>
+        <v>15.64369274785918</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.8366478355172018</v>
+        <v>0.5777961910212658</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>5.039184350880866</v>
+        <v>-0.4232510842386733</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6679</v>
+        <v>6725</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>鈺太</t>
+          <t>矽科宏晟</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>227.0480078519416</v>
+        <v>269.3087497539195</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>46.45630025690506</v>
+        <v>40.10002399456229</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>18.44206096062479</v>
+        <v>31.04235585369497</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>2.775821844819192</v>
+        <v>1.071243921483647</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>2.221960488928714</v>
+        <v>1.901786323677381</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6625</v>
+        <v>6823</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>必應</t>
+          <t>濾能</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>222.2160543957102</v>
+        <v>265.8100407292206</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>75.3</v>
+        <v>60.3</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>40.69869002750012</v>
+        <v>39.572230035947</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>9.834898928472921</v>
+        <v>20.07982889531298</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>1.102514748951951</v>
+        <v>0.6144895466539037</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.2186433779342197</v>
+        <v>-0.1288532333140821</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6485</v>
+        <v>6625</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>點序</t>
+          <t>必應</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>217.4677622102534</v>
+        <v>262.2160543957108</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>62</v>
+        <v>75.3</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>47.53178403749729</v>
+        <v>40.69869013671393</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>16.1578242790363</v>
+        <v>9.834898858368977</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1.078608696042362</v>
+        <v>1.102514748951951</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>1</v>
@@ -5923,7 +5923,7 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.4674736188439188</v>
+        <v>-0.2186433787164844</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -5933,21 +5933,21 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6560</v>
+        <v>6641</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>欣普羅</t>
+          <t>基士德-KY</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>217.0693147147454</v>
+        <v>257.9367570626847</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>31.4</v>
+        <v>17.25</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>50.88874775498218</v>
+        <v>38.76051931702429</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>15.4078587703321</v>
+        <v>7.904571489740747</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.2716117269122797</v>
+        <v>0.2552277515024079</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,11 +5976,11 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.6269876597763016</v>
+        <v>-0.0890403001282398</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
@@ -5997,7 +5997,7 @@
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>214.4561928587128</v>
+        <v>254.4561928587093</v>
       </c>
       <c r="E105" s="2" t="n">
         <v>32.75</v>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>32.06026049657144</v>
+        <v>32.06026057639045</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>25.54604546409276</v>
+        <v>25.546045215459</v>
       </c>
       <c r="J105" s="2" t="n">
         <v>1.02969644548787</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,7 +6029,7 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.4954504907077975</v>
+        <v>-0.4954504915091358</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6039,21 +6039,21 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6803</v>
+        <v>6558</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>崑鼎</t>
+          <t>興能高</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>211.5241184065813</v>
+        <v>254.2977921424391</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>270.5</v>
+        <v>24.75</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>49.00059484890273</v>
+        <v>42.81023828242077</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>17.99469489582995</v>
+        <v>26.47946318360539</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.2863516570171616</v>
+        <v>0.6322989920657168</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.4263647617013814</v>
+        <v>0.0495044904920867</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6556</v>
+        <v>6776</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>勝品</t>
+          <t>展碁國際</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>210.1324785409812</v>
+        <v>244.1328458207486</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>61.3</v>
+        <v>53.1</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>46.56761675044798</v>
+        <v>44.08059857506305</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>13.74130276808536</v>
+        <v>15.39007409494405</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.1003339448129858</v>
+        <v>0.6461886850912305</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.4056283163860064</v>
+        <v>0.0055133834842318</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6643</v>
+        <v>6591</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>動力-KY</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>207.4682467098865</v>
+        <v>240.484827357201</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>407.5</v>
+        <v>42.7</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>44.16754976580877</v>
+        <v>39.1361733686368</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>10.81186101880394</v>
+        <v>28.96675883457278</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.457157582418834</v>
+        <v>0.5846792014163869</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,11 +6188,11 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.8137358745849728</v>
+        <v>0.135317968202699</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
@@ -6209,7 +6209,7 @@
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>199.3798721809744</v>
+        <v>239.3798721809744</v>
       </c>
       <c r="E109" s="2" t="n">
         <v>27</v>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>43.63845218878365</v>
+        <v>43.63845217428646</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>18.85740750405192</v>
+        <v>18.85740752425028</v>
       </c>
       <c r="J109" s="2" t="n">
         <v>0.8931413498952248</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,7 +6241,7 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.2173700301237567</v>
+        <v>-0.217370030076055</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
@@ -6251,21 +6251,21 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6552</v>
+        <v>6689</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>易華電</t>
+          <t>伊雲谷</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>198.6114796692228</v>
+        <v>235.6276962618484</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>24.25</v>
+        <v>61</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>39.43451994044883</v>
+        <v>46.90657167398356</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>13.06501073437296</v>
+        <v>13.17846069651289</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.8570402771710838</v>
+        <v>1.005749208756597</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.0317938636129511</v>
+        <v>-0.0091422425303073</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6641</v>
+        <v>6690</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>基士德-KY</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>197.9367570626847</v>
+        <v>231.5569080063362</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>17.25</v>
+        <v>162.5</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>38.76051944370148</v>
+        <v>45.00451369332657</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>7.904571499452981</v>
+        <v>9.367610184559942</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.2552277515024079</v>
+        <v>1.33617506828403</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.0890403001664013</v>
+        <v>-0.06995767283546141</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6742</v>
+        <v>6735</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>澤米</t>
+          <t>美達科技</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>197.6369803413826</v>
+        <v>230.4312222384285</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>44.95</v>
+        <v>63.3</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>49.10005228080494</v>
+        <v>45.32496343385786</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>18.68646884528517</v>
+        <v>14.88827631477854</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.8627276410185265</v>
+        <v>0.8151446085280742</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.4896770785101938</v>
+        <v>0.5866663711659492</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6689</v>
+        <v>6799</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>伊雲谷</t>
+          <t>來頡</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>195.6276962618481</v>
+        <v>226.1856229712965</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>61</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>46.90657164633706</v>
+        <v>45.46585013384726</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>13.1784606965129</v>
+        <v>11.97191411117045</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>1.005749208756597</v>
+        <v>0.6003490820651725</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.0091422424730811</v>
+        <v>0.3363242998999984</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6463,21 +6463,21 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6790</v>
+        <v>6485</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>永豐實</t>
+          <t>點序</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>193.9935584115728</v>
+        <v>217.4677622102536</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>38.15</v>
+        <v>62</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>46.78678385684766</v>
+        <v>47.53178403749729</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>11.52539886734283</v>
+        <v>16.15782423427674</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1.057074165969673</v>
+        <v>1.078608696042362</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.0470618435853021</v>
+        <v>0.4674736188629933</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6835</v>
+        <v>6606</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>圓裕</t>
+          <t>建德工業</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>191.9753779349521</v>
+        <v>216.1804676892505</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>31</v>
+        <v>25.4</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>44.27593253848839</v>
+        <v>40.41359818519551</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>14.07695306972168</v>
+        <v>11.03417276008635</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>1.56692767366099</v>
+        <v>1.220485304787023</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.1095422253462508</v>
+        <v>-0.1083231852442563</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6698</v>
+        <v>6790</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>旭暉應材</t>
+          <t>永豐實</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>186.5074331394482</v>
+        <v>213.9935584115728</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>31.5</v>
+        <v>38.15</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,16 +6594,16 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>43.23548829633543</v>
+        <v>46.78678468033092</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>18.4107714684253</v>
+        <v>11.52539922469996</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.5090116492707331</v>
+        <v>1.057074165969673</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.2194286494507724</v>
+        <v>0.0470618429938421</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6799</v>
+        <v>6803</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>來頡</t>
+          <t>崑鼎</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>186.1856229712965</v>
+        <v>211.5241184065813</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>80.59999999999999</v>
+        <v>270.5</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>45.4658500620448</v>
+        <v>49.00059496982884</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>11.97191411117044</v>
+        <v>17.99469489582995</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.6003490820651725</v>
+        <v>0.2863516570171616</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.3363243002434317</v>
+        <v>0.4263647615105816</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6498</v>
+        <v>6556</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>久禾光</t>
+          <t>勝品</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>185.6244440492424</v>
+        <v>210.1324785409812</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>75.40000000000001</v>
+        <v>61.3</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,16 +6700,16 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>47.67871131202624</v>
+        <v>46.56761680914735</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>20.16533585745767</v>
+        <v>13.74130293404726</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>1.06939364729267</v>
+        <v>0.1003339448129858</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.4642451249835677</v>
+        <v>0.4056283156609914</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6592</v>
+        <v>6643</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>和潤企業</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>178.8844887923029</v>
+        <v>207.4682467098864</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>61</v>
+        <v>407.5</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>50.26696838044881</v>
+        <v>44.16754986194621</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>10.31602160314684</v>
+        <v>10.81186108270671</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.7135983143758733</v>
+        <v>0.457157582418834</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.0046224260192142</v>
+        <v>-0.813735879354808</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6606</v>
+        <v>6835</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>建德工業</t>
+          <t>圓裕</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>176.1804676892502</v>
+        <v>191.9753779349521</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>25.4</v>
+        <v>31</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,16 +6806,16 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>40.41359814909112</v>
+        <v>44.27593357240308</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>11.03417250888237</v>
+        <v>14.07695282013767</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>1.220485304787023</v>
+        <v>1.56692767366099</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.1083231851965621</v>
+        <v>0.1095422246403122</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6671</v>
+        <v>6498</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>三能-KY</t>
+          <t>久禾光</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>174.3486770750298</v>
+        <v>185.6244440492424</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>23.2</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,16 +6859,16 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>51.13093765116963</v>
+        <v>47.67871138794328</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>16.46739665766243</v>
+        <v>20.16533594688828</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.3944688681956351</v>
+        <v>1.06939364729267</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.08115999312260209</v>
+        <v>0.464245124315785</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6534</v>
+        <v>6552</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>正瀚-創</t>
+          <t>易華電</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>171.2477959453871</v>
+        <v>168.6114796692228</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>91.09999999999999</v>
+        <v>24.25</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,16 +6912,16 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>41.70470154804806</v>
+        <v>39.43452002640186</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>11.43073393656954</v>
+        <v>13.06501080752504</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.2935142901853669</v>
+        <v>0.8570402771710838</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.1584133367574311</v>
+        <v>0.0317938635080147</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>6695</v>
+        <v>6614</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>芯鼎</t>
+          <t>資拓宏宇</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>168.9260411213474</v>
+        <v>166.1471815895175</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>49.5</v>
+        <v>35.35</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,16 +6965,16 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>49.19785743846517</v>
+        <v>34.42667213684626</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>13.39133524751905</v>
+        <v>10.29338433554352</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.4674290607110941</v>
+        <v>0.8570889589565311</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.3553813040902324</v>
+        <v>0.0482677396347225</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>6546</v>
+        <v>6698</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>正基</t>
+          <t>旭暉應材</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>146.3625014098476</v>
+        <v>156.5074331394484</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>62.5</v>
+        <v>31.5</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>49.14691757208266</v>
+        <v>43.23548811531437</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>15.36928136833898</v>
+        <v>18.41077153251337</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.754615596011122</v>
+        <v>0.5090116492707331</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>1</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.0664109925208464</v>
+        <v>0.219428650042233</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>6614</v>
+        <v>6504</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>資拓宏宇</t>
+          <t>南六</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>146.147181589518</v>
+        <v>149.3996636682241</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>35.35</v>
+        <v>37.1</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>34.42667177198545</v>
+        <v>42.52913940312992</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>10.29338437109069</v>
+        <v>12.51777644886116</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.8570889589565311</v>
+        <v>0.9021219195432986</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>0.0482677398064324</v>
+        <v>-0.1074848441968173</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7099,21 +7099,21 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>6504</v>
+        <v>6546</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>南六</t>
+          <t>正基</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>129.3996636682242</v>
+        <v>146.3625014098476</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>37.1</v>
+        <v>62.5</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,16 +7124,16 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>42.5291393807215</v>
+        <v>49.14691767058797</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>12.51777641425455</v>
+        <v>15.36928144971952</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.9021219195432986</v>
+        <v>0.754615596011122</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L126" s="2" t="n">
         <v>0</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.1074848441204996</v>
+        <v>0.0664109921201759</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7177,10 +7177,10 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>51.94846003024985</v>
+        <v>51.94846002255518</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>6.559576702405057</v>
+        <v>6.559576899034672</v>
       </c>
       <c r="J127" s="2" t="n">
         <v>0.1138113823753177</v>
@@ -7195,7 +7195,7 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.2344218334562261</v>
+        <v>-0.2344218334848475</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
@@ -7230,10 +7230,10 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>39.3527288374986</v>
+        <v>39.35272896840105</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>17.93043189120777</v>
+        <v>17.93043187712296</v>
       </c>
       <c r="J128" s="2" t="n">
         <v>0.718688385756441</v>
@@ -7248,7 +7248,7 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>0.5801269309263137</v>
+        <v>0.5801269299723266</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
